--- a/excel/湖南仓 - 副本.xlsx
+++ b/excel/湖南仓 - 副本.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kaoshi\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kaoshi\new\qiancheng0605v1\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ECCAF7-60E9-456B-81E3-8CF630C5ADC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC52A32-EECC-4142-854B-F01C38ECDFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>蘸料调料</t>
   </si>
   <si>
-    <t>ZBWP0127</t>
-  </si>
-  <si>
     <t>尹三顺秘制蘸料（特辣）</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>18900770808</t>
+  </si>
+  <si>
+    <t>SKU_01497</t>
   </si>
 </sst>
 </file>
@@ -958,29 +958,29 @@
         <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -989,40 +989,40 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="AF3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
